--- a/InputData/web-app/BCF/BTU Conversion Factors.xlsx
+++ b/InputData/web-app/BCF/BTU Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/users/aaggarwal/library/containers/com.microsoft.excel/data/state-eps-data-repository/template_state_3.3/web-app/bcf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shelley\Dropbox (Energy Innovation)\PC (2)\Documents\GitHub_Repositories\eps-us\InputData\web-app\BCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76952F9-3660-0F42-932E-7660B4B2CD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8A7001-1A9D-42BC-A0B1-892F751D4320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15345" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -3486,7 +3486,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3885,7 +3885,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4320,40 +4319,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.36328125" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" customWidth="1"/>
+    <col min="3" max="3" width="39.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" s="208">
-        <v>44631</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -4362,152 +4358,152 @@
       </c>
       <c r="C6" s="202"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" s="196" t="s">
         <v>401</v>
       </c>
       <c r="C13" s="202"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="198" t="s">
         <v>331</v>
       </c>
       <c r="B40" s="199"/>
     </row>
-    <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="203" t="s">
         <v>349</v>
       </c>
@@ -4518,7 +4514,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="201" t="s">
         <v>392</v>
       </c>
@@ -4526,7 +4522,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="197" t="s">
         <v>324</v>
       </c>
@@ -4534,7 +4530,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="197" t="s">
         <v>366</v>
       </c>
@@ -4542,7 +4538,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="201" t="s">
         <v>387</v>
       </c>
@@ -4550,7 +4546,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="201" t="s">
         <v>389</v>
       </c>
@@ -4558,7 +4554,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="201" t="s">
         <v>356</v>
       </c>
@@ -4569,16 +4565,16 @@
         <v>360</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="201"/>
     </row>
-    <row r="49" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="198" t="s">
         <v>336</v>
       </c>
       <c r="B49" s="199"/>
     </row>
-    <row r="50" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="203" t="s">
         <v>349</v>
       </c>
@@ -4586,7 +4582,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="51" spans="1:2" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="201" t="s">
         <v>392</v>
       </c>
@@ -4594,7 +4590,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="52" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="197" t="s">
         <v>324</v>
       </c>
@@ -4602,7 +4598,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="53" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="197" t="s">
         <v>366</v>
       </c>
@@ -4610,7 +4606,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="54" spans="1:2" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="201" t="s">
         <v>391</v>
       </c>
@@ -4618,7 +4614,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="55" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="201" t="s">
         <v>388</v>
       </c>
@@ -4626,7 +4622,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="56" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="201" t="s">
         <v>354</v>
       </c>
@@ -4634,37 +4630,37 @@
         <v>355</v>
       </c>
     </row>
-    <row r="57" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="198" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="59" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="60" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="198" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="62" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="63" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="196" t="s">
         <v>316</v>
       </c>
       <c r="B65" s="202"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="200">
         <v>42</v>
       </c>
@@ -4672,7 +4668,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <f>3.142*10^6</f>
         <v>3142000</v>
@@ -4690,14 +4686,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK85"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" style="7" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="9.1640625" style="7"/>
+    <col min="1" max="1" width="20.81640625" style="7" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7265625" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
         <v>386</v>
       </c>
@@ -4804,8 +4800,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="20" t="s">
         <v>121</v>
       </c>
@@ -4816,7 +4812,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="20" t="s">
         <v>120</v>
       </c>
@@ -4829,7 +4825,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="20" t="s">
         <v>118</v>
       </c>
@@ -4840,7 +4836,7 @@
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="20" t="s">
         <v>117</v>
       </c>
@@ -4851,7 +4847,7 @@
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
     </row>
-    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>116</v>
       </c>
@@ -4859,12 +4855,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>2</v>
       </c>
@@ -4974,7 +4970,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="16" t="s">
         <v>2</v>
       </c>
@@ -5084,17 +5080,17 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:37" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>114</v>
       </c>
@@ -5207,7 +5203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>113</v>
       </c>
@@ -5320,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>112</v>
       </c>
@@ -5433,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>111</v>
       </c>
@@ -5546,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>110</v>
       </c>
@@ -5659,7 +5655,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>109</v>
       </c>
@@ -5772,7 +5768,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>108</v>
       </c>
@@ -5885,7 +5881,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>107</v>
       </c>
@@ -5998,7 +5994,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>106</v>
       </c>
@@ -6111,7 +6107,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>105</v>
       </c>
@@ -6224,7 +6220,7 @@
         <v>-1.1E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>104</v>
       </c>
@@ -6337,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>103</v>
       </c>
@@ -6450,7 +6446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>102</v>
       </c>
@@ -6563,7 +6559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>100</v>
       </c>
@@ -6676,7 +6672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>99</v>
       </c>
@@ -6789,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>98</v>
       </c>
@@ -6902,7 +6898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>97</v>
       </c>
@@ -7015,7 +7011,7 @@
         <v>-2.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>96</v>
       </c>
@@ -7128,7 +7124,7 @@
         <v>-2.1599999999999999E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>95</v>
       </c>
@@ -7241,7 +7237,7 @@
         <v>-2.2499999999999999E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>379</v>
       </c>
@@ -7354,7 +7350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>377</v>
       </c>
@@ -7467,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>94</v>
       </c>
@@ -7580,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>93</v>
       </c>
@@ -7693,7 +7689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>92</v>
       </c>
@@ -7806,7 +7802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>91</v>
       </c>
@@ -7919,7 +7915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>90</v>
       </c>
@@ -8032,7 +8028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>89</v>
       </c>
@@ -8145,7 +8141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>88</v>
       </c>
@@ -8258,7 +8254,7 @@
         <v>1.9699999999999999E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>87</v>
       </c>
@@ -8371,7 +8367,7 @@
         <v>-4.8299999999999998E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>86</v>
       </c>
@@ -8484,7 +8480,7 @@
         <v>-3.1150000000000001E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>85</v>
       </c>
@@ -8597,12 +8593,12 @@
         <v>-1.013E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>84</v>
       </c>
@@ -8715,7 +8711,7 @@
         <v>-2.4000000000000001E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>83</v>
       </c>
@@ -8828,7 +8824,7 @@
         <v>-3.0000000000000001E-6</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>82</v>
       </c>
@@ -8941,7 +8937,7 @@
         <v>2.3E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>81</v>
       </c>
@@ -9054,12 +9050,12 @@
         <v>-2.7700000000000001E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>80</v>
       </c>
@@ -9172,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>79</v>
       </c>
@@ -9285,7 +9281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>78</v>
       </c>
@@ -9398,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>77</v>
       </c>
@@ -9511,7 +9507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>76</v>
       </c>
@@ -9624,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>75</v>
       </c>
@@ -9737,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>74</v>
       </c>
@@ -9850,12 +9846,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>73</v>
       </c>
@@ -9968,7 +9964,7 @@
         <v>-1.4100000000000001E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>72</v>
       </c>
@@ -10081,7 +10077,7 @@
         <v>-1.0139999999999999E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>71</v>
       </c>
@@ -10194,7 +10190,7 @@
         <v>-2.1699999999999999E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>70</v>
       </c>
@@ -10307,7 +10303,7 @@
         <v>2.8499999999999999E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>69</v>
       </c>
@@ -10420,7 +10416,7 @@
         <v>2.3E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>68</v>
       </c>
@@ -10533,7 +10529,7 @@
         <v>-5.5000000000000002E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>67</v>
       </c>
@@ -10646,7 +10642,7 @@
         <v>-9.5000000000000005E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>66</v>
       </c>
@@ -10759,7 +10755,7 @@
         <v>2.5799999999999998E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>65</v>
       </c>
@@ -10872,7 +10868,7 @@
         <v>5.7700000000000004E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>64</v>
       </c>
@@ -10985,7 +10981,7 @@
         <v>-1.2830000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>63</v>
       </c>
@@ -11098,7 +11094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>62</v>
       </c>
@@ -11211,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>61</v>
       </c>
@@ -11324,78 +11320,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B78" s="209" t="s">
+    <row r="77" spans="1:37" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="208" t="s">
         <v>57</v>
       </c>
-      <c r="C78" s="209"/>
-      <c r="D78" s="209"/>
-      <c r="E78" s="209"/>
-      <c r="F78" s="209"/>
-      <c r="G78" s="209"/>
-      <c r="H78" s="209"/>
-      <c r="I78" s="209"/>
-      <c r="J78" s="209"/>
-      <c r="K78" s="209"/>
-      <c r="L78" s="209"/>
-      <c r="M78" s="209"/>
-      <c r="N78" s="209"/>
-      <c r="O78" s="209"/>
-      <c r="P78" s="209"/>
-      <c r="Q78" s="209"/>
-      <c r="R78" s="209"/>
-      <c r="S78" s="209"/>
-      <c r="T78" s="209"/>
-      <c r="U78" s="209"/>
-      <c r="V78" s="209"/>
-      <c r="W78" s="209"/>
-      <c r="X78" s="209"/>
-      <c r="Y78" s="209"/>
-      <c r="Z78" s="209"/>
-      <c r="AA78" s="209"/>
-      <c r="AB78" s="209"/>
-      <c r="AC78" s="209"/>
-      <c r="AD78" s="209"/>
-      <c r="AE78" s="209"/>
-      <c r="AF78" s="209"/>
-      <c r="AG78" s="209"/>
-      <c r="AH78" s="209"/>
-      <c r="AI78" s="209"/>
-      <c r="AJ78" s="209"/>
-      <c r="AK78" s="209"/>
-    </row>
-    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C78" s="208"/>
+      <c r="D78" s="208"/>
+      <c r="E78" s="208"/>
+      <c r="F78" s="208"/>
+      <c r="G78" s="208"/>
+      <c r="H78" s="208"/>
+      <c r="I78" s="208"/>
+      <c r="J78" s="208"/>
+      <c r="K78" s="208"/>
+      <c r="L78" s="208"/>
+      <c r="M78" s="208"/>
+      <c r="N78" s="208"/>
+      <c r="O78" s="208"/>
+      <c r="P78" s="208"/>
+      <c r="Q78" s="208"/>
+      <c r="R78" s="208"/>
+      <c r="S78" s="208"/>
+      <c r="T78" s="208"/>
+      <c r="U78" s="208"/>
+      <c r="V78" s="208"/>
+      <c r="W78" s="208"/>
+      <c r="X78" s="208"/>
+      <c r="Y78" s="208"/>
+      <c r="Z78" s="208"/>
+      <c r="AA78" s="208"/>
+      <c r="AB78" s="208"/>
+      <c r="AC78" s="208"/>
+      <c r="AD78" s="208"/>
+      <c r="AE78" s="208"/>
+      <c r="AF78" s="208"/>
+      <c r="AG78" s="208"/>
+      <c r="AH78" s="208"/>
+      <c r="AI78" s="208"/>
+      <c r="AJ78" s="208"/>
+      <c r="AK78" s="208"/>
+    </row>
+    <row r="79" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8" t="s">
         <v>372</v>
       </c>
@@ -11412,40 +11408,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" style="22" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="22" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1640625" style="22"/>
-    <col min="11" max="11" width="10.33203125" style="22" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.1640625" style="22"/>
-    <col min="15" max="15" width="12.83203125" style="22" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="9.1640625" style="22"/>
-    <col min="19" max="19" width="10.33203125" style="22" customWidth="1"/>
-    <col min="20" max="22" width="9.1640625" style="22"/>
-    <col min="23" max="23" width="10.6640625" style="22" customWidth="1"/>
-    <col min="24" max="16384" width="9.1640625" style="22"/>
+    <col min="1" max="1" width="33.08984375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" style="22" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="22"/>
+    <col min="11" max="11" width="10.36328125" style="22" customWidth="1"/>
+    <col min="12" max="12" width="12.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.08984375" style="22"/>
+    <col min="15" max="15" width="12.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="9.08984375" style="22"/>
+    <col min="19" max="19" width="10.36328125" style="22" customWidth="1"/>
+    <col min="20" max="22" width="9.08984375" style="22"/>
+    <col min="23" max="23" width="10.7265625" style="22" customWidth="1"/>
+    <col min="24" max="16384" width="9.08984375" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="24" t="s">
         <v>126</v>
       </c>
@@ -11468,7 +11464,7 @@
       </c>
       <c r="I3" s="29"/>
     </row>
-    <row r="4" spans="1:23" ht="29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A4" s="30"/>
       <c r="B4" s="31" t="s">
         <v>302</v>
@@ -11493,7 +11489,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" s="35" t="s">
         <v>137</v>
       </c>
@@ -11510,7 +11506,7 @@
       <c r="H5" s="39"/>
       <c r="I5" s="40"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="41" t="s">
         <v>139</v>
       </c>
@@ -11535,7 +11531,7 @@
       <c r="T6" s="47"/>
       <c r="V6" s="47"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="48" t="s">
         <v>142</v>
       </c>
@@ -11572,7 +11568,7 @@
       <c r="V7" s="55"/>
       <c r="W7" s="55"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="48" t="s">
         <v>143</v>
       </c>
@@ -11609,7 +11605,7 @@
       <c r="V8" s="55"/>
       <c r="W8" s="55"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="48" t="s">
         <v>144</v>
       </c>
@@ -11646,7 +11642,7 @@
       <c r="V9" s="55"/>
       <c r="W9" s="55"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="48" t="s">
         <v>145</v>
       </c>
@@ -11679,7 +11675,7 @@
       <c r="V10" s="55"/>
       <c r="W10" s="55"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="48" t="s">
         <v>146</v>
       </c>
@@ -11720,7 +11716,7 @@
       <c r="V11" s="55"/>
       <c r="W11" s="55"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="48" t="s">
         <v>147</v>
       </c>
@@ -11757,7 +11753,7 @@
       <c r="R12" s="55"/>
       <c r="S12" s="55"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>148</v>
       </c>
@@ -11786,7 +11782,7 @@
         <v>0.93726057101554028</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>149</v>
       </c>
@@ -11815,7 +11811,7 @@
         <v>0.93726057101554017</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="48" t="s">
         <v>150</v>
       </c>
@@ -11853,7 +11849,7 @@
       <c r="V15" s="65"/>
       <c r="W15" s="61"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="48" t="s">
         <v>151</v>
       </c>
@@ -11887,7 +11883,7 @@
       <c r="V16" s="65"/>
       <c r="W16" s="61"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="48" t="s">
         <v>152</v>
       </c>
@@ -11925,7 +11921,7 @@
       <c r="V17" s="65"/>
       <c r="W17" s="61"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="48" t="s">
         <v>153</v>
       </c>
@@ -11959,7 +11955,7 @@
       <c r="V18" s="65"/>
       <c r="W18" s="61"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="48" t="s">
         <v>154</v>
       </c>
@@ -11993,7 +11989,7 @@
       <c r="M19" s="65"/>
       <c r="N19" s="61"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="67" t="s">
         <v>303</v>
       </c>
@@ -12024,7 +12020,7 @@
       <c r="O20" s="55"/>
       <c r="W20" s="61"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" s="68" t="s">
         <v>406</v>
       </c>
@@ -12051,7 +12047,7 @@
       </c>
       <c r="I21" s="54"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="48" t="s">
         <v>155</v>
       </c>
@@ -12080,7 +12076,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="48" t="s">
         <v>156</v>
       </c>
@@ -12109,7 +12105,7 @@
         <v>0.93499781627602274</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" s="48" t="s">
         <v>157</v>
       </c>
@@ -12138,7 +12134,7 @@
         <v>0.93476175247841387</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" s="70" t="s">
         <v>407</v>
       </c>
@@ -12167,7 +12163,7 @@
         <v>0.93404711473172097</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" s="71" t="s">
         <v>158</v>
       </c>
@@ -12196,7 +12192,7 @@
         <v>0.93500003751584637</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" s="71" t="s">
         <v>159</v>
       </c>
@@ -12225,7 +12221,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" s="71" t="s">
         <v>160</v>
       </c>
@@ -12255,7 +12251,7 @@
       </c>
       <c r="J28" s="73"/>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" s="71" t="s">
         <v>161</v>
       </c>
@@ -12284,7 +12280,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" s="71" t="s">
         <v>162</v>
       </c>
@@ -12313,7 +12309,7 @@
         <v>0.93499781627602263</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" s="71" t="s">
         <v>163</v>
       </c>
@@ -12343,7 +12339,7 @@
       </c>
       <c r="J31" s="73"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" s="71" t="s">
         <v>164</v>
       </c>
@@ -12372,7 +12368,7 @@
         <v>0.90299302022950434</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="71" t="s">
         <v>165</v>
       </c>
@@ -12402,7 +12398,7 @@
       </c>
       <c r="J33" s="73"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="71" t="s">
         <v>166</v>
       </c>
@@ -12431,7 +12427,7 @@
         <v>0.92867915675168411</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="71" t="s">
         <v>167</v>
       </c>
@@ -12461,7 +12457,7 @@
       </c>
       <c r="J35" s="73"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="71" t="s">
         <v>168</v>
       </c>
@@ -12491,7 +12487,7 @@
       </c>
       <c r="J36" s="73"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="71" t="s">
         <v>169</v>
       </c>
@@ -12521,7 +12517,7 @@
       </c>
       <c r="J37" s="73"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="71" t="s">
         <v>170</v>
       </c>
@@ -12551,7 +12547,7 @@
       </c>
       <c r="J38" s="73"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="71" t="s">
         <v>171</v>
       </c>
@@ -12582,7 +12578,7 @@
       <c r="J39" s="73"/>
       <c r="K39" s="73"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="71" t="s">
         <v>172</v>
       </c>
@@ -12613,7 +12609,7 @@
       <c r="J40" s="73"/>
       <c r="K40" s="73"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="71" t="s">
         <v>173</v>
       </c>
@@ -12643,7 +12639,7 @@
       </c>
       <c r="K41" s="73"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="70" t="s">
         <v>174</v>
       </c>
@@ -12673,7 +12669,7 @@
       </c>
       <c r="K42" s="73"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="70" t="s">
         <v>175</v>
       </c>
@@ -12703,7 +12699,7 @@
       </c>
       <c r="K43" s="73"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="71" t="s">
         <v>176</v>
       </c>
@@ -12733,7 +12729,7 @@
       </c>
       <c r="K44" s="73"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
         <v>177</v>
       </c>
@@ -12762,7 +12758,7 @@
         <v>0.93361506882395562</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="71" t="s">
         <v>178</v>
       </c>
@@ -12792,7 +12788,7 @@
       </c>
       <c r="K46" s="73"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="48" t="s">
         <v>408</v>
       </c>
@@ -12821,7 +12817,7 @@
         <v>0.93361506882395551</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="48" t="s">
         <v>179</v>
       </c>
@@ -12850,7 +12846,7 @@
         <v>0.93500003751584626</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="48" t="s">
         <v>180</v>
       </c>
@@ -12880,7 +12876,7 @@
       </c>
       <c r="J49" s="73"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="48" t="s">
         <v>181</v>
       </c>
@@ -12910,7 +12906,7 @@
       </c>
       <c r="J50" s="73"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="48" t="s">
         <v>182</v>
       </c>
@@ -12940,7 +12936,7 @@
       </c>
       <c r="J51" s="73"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="48" t="s">
         <v>183</v>
       </c>
@@ -12970,7 +12966,7 @@
       </c>
       <c r="J52" s="73"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="48" t="s">
         <v>184</v>
       </c>
@@ -13000,7 +12996,7 @@
       </c>
       <c r="J53" s="73"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="48" t="s">
         <v>185</v>
       </c>
@@ -13030,7 +13026,7 @@
       </c>
       <c r="J54" s="73"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="48" t="s">
         <v>186</v>
       </c>
@@ -13060,7 +13056,7 @@
       </c>
       <c r="J55" s="73"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="67" t="s">
         <v>187</v>
       </c>
@@ -13089,7 +13085,7 @@
         <v>0.92157077225989936</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="48" t="s">
         <v>188</v>
       </c>
@@ -13116,7 +13112,7 @@
         <v>0.92932939503336609</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="41" t="s">
         <v>189</v>
       </c>
@@ -13145,7 +13141,7 @@
         <v>0.93722267739953979</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="48" t="s">
         <v>191</v>
       </c>
@@ -13168,7 +13164,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="67" t="s">
         <v>194</v>
       </c>
@@ -13197,7 +13193,7 @@
         <v>0.90266299357208446</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="48" t="s">
         <v>195</v>
       </c>
@@ -13227,7 +13223,7 @@
       </c>
       <c r="L61" s="47"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="48" t="s">
         <v>196</v>
       </c>
@@ -13256,7 +13252,7 @@
         <v>0.84548104956268222</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="71" t="s">
         <v>197</v>
       </c>
@@ -13277,7 +13273,7 @@
       </c>
       <c r="I63" s="54"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="41" t="s">
         <v>190</v>
       </c>
@@ -13307,7 +13303,7 @@
       </c>
       <c r="K64" s="47"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="67" t="s">
         <v>198</v>
       </c>
@@ -13328,7 +13324,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="68" t="s">
         <v>200</v>
       </c>
@@ -13354,7 +13350,7 @@
       <c r="I66" s="94"/>
       <c r="K66" s="95"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="68" t="s">
         <v>201</v>
       </c>
@@ -13382,7 +13378,7 @@
       </c>
       <c r="K67" s="95"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="68" t="s">
         <v>202</v>
       </c>
@@ -13410,7 +13406,7 @@
       </c>
       <c r="K68" s="95"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="68" t="s">
         <v>203</v>
       </c>
@@ -13438,7 +13434,7 @@
       </c>
       <c r="K69" s="95"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="68" t="s">
         <v>204</v>
       </c>
@@ -13467,7 +13463,7 @@
       <c r="K70" s="95"/>
       <c r="M70" s="73"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="71" t="s">
         <v>205</v>
       </c>
@@ -13496,7 +13492,7 @@
       <c r="K71" s="95"/>
       <c r="L71" s="95"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="70" t="s">
         <v>206</v>
       </c>
@@ -13524,7 +13520,7 @@
       </c>
       <c r="K72" s="95"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="48" t="s">
         <v>207</v>
       </c>
@@ -13551,7 +13547,7 @@
         <v>0.94242199100000001</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="48" t="s">
         <v>208</v>
       </c>
@@ -13579,7 +13575,7 @@
       </c>
       <c r="K74" s="97"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="48" t="s">
         <v>409</v>
       </c>
@@ -13607,7 +13603,7 @@
       </c>
       <c r="K75" s="97"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="48" t="s">
         <v>209</v>
       </c>
@@ -13634,7 +13630,7 @@
         <v>0.93173565722585328</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="70" t="s">
         <v>210</v>
       </c>
@@ -13663,7 +13659,7 @@
       <c r="J77" s="55"/>
       <c r="K77" s="98"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="71" t="s">
         <v>211</v>
       </c>
@@ -13691,7 +13687,7 @@
       </c>
       <c r="K78" s="97"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="71" t="s">
         <v>212</v>
       </c>
@@ -13718,7 +13714,7 @@
         <v>0.93680161201685286</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="71" t="s">
         <v>213</v>
       </c>
@@ -13745,7 +13741,7 @@
         <v>0.93292760238366934</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="71" t="s">
         <v>214</v>
       </c>
@@ -13772,7 +13768,7 @@
         <v>0.96554227633195577</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="71" t="s">
         <v>410</v>
       </c>
@@ -13799,7 +13795,7 @@
         <v>0.93359512366662756</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="99" t="s">
         <v>215</v>
       </c>
@@ -13822,7 +13818,7 @@
       </c>
       <c r="I83" s="102"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="103" t="s">
         <v>216</v>
       </c>
@@ -13845,7 +13841,7 @@
         <v>0.85292563033160751</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="103" t="s">
         <v>217</v>
       </c>
@@ -13868,7 +13864,7 @@
         <v>0.88047037071579148</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="103" t="s">
         <v>218</v>
       </c>
@@ -13895,7 +13891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="106" t="s">
         <v>219</v>
       </c>
@@ -13922,7 +13918,7 @@
         <v>0.90447216306662592</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="107" t="s">
         <v>220</v>
       </c>
@@ -13949,7 +13945,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="89" spans="1:14" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="73" t="s">
         <v>221</v>
       </c>
@@ -13976,7 +13972,7 @@
         <v>0.94150280898876404</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="23" t="s">
         <v>222</v>
       </c>
@@ -14003,7 +13999,7 @@
         <v>0.8252427184466018</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="73" t="s">
         <v>223</v>
       </c>
@@ -14030,7 +14026,7 @@
         <v>0.87681159420289856</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="118" t="s">
         <v>411</v>
       </c>
@@ -14064,7 +14060,7 @@
       <c r="M92" s="121"/>
       <c r="N92" s="122"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="123" t="s">
         <v>412</v>
       </c>
@@ -14090,12 +14086,12 @@
       <c r="M93" s="125"/>
       <c r="N93" s="126"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="127"/>
       <c r="B94" s="128"/>
       <c r="N94" s="129"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="127" t="s">
         <v>224</v>
       </c>
@@ -14110,7 +14106,7 @@
       <c r="M95" s="73"/>
       <c r="N95" s="129"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="130" t="s">
         <v>225</v>
       </c>
@@ -14128,7 +14124,7 @@
       <c r="M96" s="133"/>
       <c r="N96" s="134"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="135" t="s">
         <v>226</v>
       </c>
@@ -14172,7 +14168,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="136" t="s">
         <v>233</v>
       </c>
@@ -14216,7 +14212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="137" t="s">
         <v>234</v>
       </c>
@@ -14260,7 +14256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="123" t="s">
         <v>235</v>
       </c>
@@ -14304,7 +14300,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="127" t="s">
         <v>236</v>
       </c>
@@ -14348,13 +14344,13 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="127"/>
       <c r="B102" s="128"/>
       <c r="F102" s="73"/>
       <c r="G102" s="129"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="127" t="s">
         <v>237</v>
       </c>
@@ -14363,7 +14359,7 @@
       <c r="F103" s="73"/>
       <c r="G103" s="129"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="127" t="s">
         <v>238</v>
       </c>
@@ -14386,7 +14382,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="130" t="s">
         <v>233</v>
       </c>
@@ -14407,7 +14403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="22" t="s">
         <v>242</v>
       </c>
@@ -14430,7 +14426,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="23" t="s">
         <v>243</v>
       </c>
@@ -14453,7 +14449,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="118" t="s">
         <v>244</v>
       </c>
@@ -14476,7 +14472,7 @@
         <v>-87</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="127" t="s">
         <v>245</v>
       </c>
@@ -14499,7 +14495,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="127" t="s">
         <v>246</v>
       </c>
@@ -14522,17 +14518,17 @@
         <v>-71</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="127"/>
       <c r="B111" s="146"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="130" t="s">
         <v>247</v>
       </c>
       <c r="B112" s="147"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113" s="22" t="s">
         <v>248</v>
       </c>
@@ -14540,7 +14536,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114" s="148" t="s">
         <v>249</v>
       </c>
@@ -14550,7 +14546,7 @@
       <c r="C114" s="73"/>
       <c r="D114" s="73"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115" s="73" t="s">
         <v>250</v>
       </c>
@@ -14558,7 +14554,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116" s="22" t="s">
         <v>251</v>
       </c>
@@ -14571,7 +14567,7 @@
       <c r="R116" s="151"/>
       <c r="V116" s="151"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117" s="22" t="s">
         <v>252</v>
       </c>
@@ -14584,7 +14580,7 @@
       <c r="R117" s="154"/>
       <c r="V117" s="154"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B118" s="155"/>
       <c r="C118" s="156"/>
       <c r="D118" s="157"/>
@@ -14604,7 +14600,7 @@
       <c r="W118" s="158"/>
       <c r="X118" s="157"/>
     </row>
-    <row r="119" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="73" t="s">
         <v>253</v>
       </c>
@@ -14627,7 +14623,7 @@
       <c r="W119" s="160"/>
       <c r="X119" s="161"/>
     </row>
-    <row r="120" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B120" s="162"/>
       <c r="C120" s="163"/>
       <c r="D120" s="164"/>
@@ -14647,7 +14643,7 @@
       <c r="W120" s="163"/>
       <c r="X120" s="164"/>
     </row>
-    <row r="121" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B121" s="162">
         <v>10</v>
       </c>
@@ -14679,7 +14675,7 @@
       <c r="W121" s="163"/>
       <c r="X121" s="164"/>
     </row>
-    <row r="122" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B122" s="162">
         <v>10</v>
       </c>
@@ -14711,7 +14707,7 @@
       <c r="W122" s="163"/>
       <c r="X122" s="164"/>
     </row>
-    <row r="123" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B123" s="162" t="s">
         <v>254</v>
       </c>
@@ -14767,7 +14763,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="124" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B124" s="162">
         <v>1990</v>
       </c>
@@ -14823,7 +14819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" s="73" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B125" s="162">
         <v>1995</v>
       </c>
@@ -14879,7 +14875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B126" s="168">
         <v>2000</v>
       </c>
@@ -14935,7 +14931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B127" s="22">
         <v>2005</v>
       </c>
@@ -14991,7 +14987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A128" s="148"/>
       <c r="B128" s="22">
         <v>2010</v>
@@ -15048,7 +15044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A129" s="171"/>
       <c r="B129" s="172">
         <v>2015</v>
@@ -15106,7 +15102,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A130" s="175"/>
       <c r="B130" s="176">
         <v>2017</v>
@@ -15164,7 +15160,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A131" s="175"/>
       <c r="B131" s="179">
         <v>2020</v>
@@ -15180,7 +15176,7 @@
       <c r="G131" s="174"/>
       <c r="H131" s="174"/>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A132" s="175"/>
       <c r="B132" s="179"/>
       <c r="C132" s="179"/>
@@ -15190,7 +15186,7 @@
       <c r="G132" s="174"/>
       <c r="H132" s="174"/>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="175" t="s">
         <v>262</v>
       </c>
@@ -15202,7 +15198,7 @@
       <c r="G133" s="174"/>
       <c r="H133" s="174"/>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" s="181" t="s">
         <v>263</v>
       </c>
@@ -15224,7 +15220,7 @@
       <c r="G134" s="174"/>
       <c r="H134" s="174"/>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="174" t="s">
         <v>269</v>
       </c>
@@ -15246,7 +15242,7 @@
       <c r="G135" s="174"/>
       <c r="H135" s="174"/>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136" s="171" t="s">
         <v>270</v>
       </c>
@@ -15268,7 +15264,7 @@
       <c r="G136" s="174"/>
       <c r="H136" s="174"/>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137" s="175" t="s">
         <v>271</v>
       </c>
@@ -15290,7 +15286,7 @@
       <c r="G137" s="174"/>
       <c r="H137" s="174"/>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138" s="175" t="s">
         <v>272</v>
       </c>
@@ -15312,7 +15308,7 @@
       <c r="G138" s="174"/>
       <c r="H138" s="174"/>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139" s="175" t="s">
         <v>273</v>
       </c>
@@ -15334,7 +15330,7 @@
       <c r="G139" s="174"/>
       <c r="H139" s="174"/>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A140" s="175"/>
       <c r="B140" s="163"/>
       <c r="C140" s="179"/>
@@ -15344,7 +15340,7 @@
       <c r="G140" s="174"/>
       <c r="H140" s="174"/>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A141" s="181" t="s">
         <v>274</v>
       </c>
@@ -15366,7 +15362,7 @@
       <c r="G141" s="174"/>
       <c r="H141" s="174"/>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A142" s="174" t="s">
         <v>280</v>
       </c>
@@ -15388,7 +15384,7 @@
       <c r="G142" s="174"/>
       <c r="H142" s="174"/>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A143" s="171" t="s">
         <v>281</v>
       </c>
@@ -15411,7 +15407,7 @@
       <c r="H143" s="172"/>
       <c r="I143" s="190"/>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A144" s="175" t="s">
         <v>282</v>
       </c>
@@ -15434,7 +15430,7 @@
       <c r="H144" s="176"/>
       <c r="I144" s="129"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="175" t="s">
         <v>283</v>
       </c>
@@ -15457,7 +15453,7 @@
       <c r="H145" s="176"/>
       <c r="I145" s="129"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="175" t="s">
         <v>284</v>
       </c>
@@ -15480,7 +15476,7 @@
       <c r="H146" s="176"/>
       <c r="I146" s="129"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="175"/>
       <c r="B147" s="179"/>
       <c r="C147" s="177"/>
@@ -15491,7 +15487,7 @@
       <c r="H147" s="176"/>
       <c r="I147" s="129"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="175" t="s">
         <v>285</v>
       </c>
@@ -15520,7 +15516,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="175" t="s">
         <v>294</v>
       </c>
@@ -15549,7 +15545,7 @@
         <v>2684519.5376862194</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="175" t="s">
         <v>295</v>
       </c>
@@ -15578,7 +15574,7 @@
         <v>2684.5195376862198</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="195" t="s">
         <v>296</v>
       </c>
@@ -15607,7 +15603,7 @@
         <v>2.6845195376862194</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="22" t="s">
         <v>297</v>
       </c>
@@ -15636,7 +15632,7 @@
         <v>745.69987157950538</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="22" t="s">
         <v>298</v>
       </c>
@@ -15665,7 +15661,7 @@
         <v>0.74569987157950535</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="22" t="s">
         <v>299</v>
       </c>
@@ -15694,7 +15690,7 @@
         <v>2544.4335839531336</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="22" t="s">
         <v>300</v>
       </c>
@@ -15723,7 +15719,7 @@
         <v>2.5444335839531337E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="22" t="s">
         <v>301</v>
       </c>
@@ -15752,7 +15748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="22" t="s">
         <v>413</v>
       </c>
@@ -15772,7 +15768,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="22" t="s">
         <v>414</v>
       </c>
@@ -15792,7 +15788,7 @@
         <v>1609340</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="22" t="s">
         <v>415</v>
       </c>
@@ -15812,7 +15808,7 @@
         <v>1609.34</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="22" t="s">
         <v>416</v>
       </c>
@@ -15832,7 +15828,7 @@
         <v>1.60934</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="22" t="s">
         <v>417</v>
       </c>
@@ -15852,7 +15848,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="22" t="s">
         <v>418</v>
       </c>
@@ -15901,14 +15897,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.81640625" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="35" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>404</v>
       </c>
@@ -16015,7 +16011,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>346</v>
       </c>
@@ -16156,7 +16152,7 @@
         <v>3142000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>323</v>
       </c>
@@ -16297,7 +16293,7 @@
         <v>19887484000000</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>324</v>
       </c>
@@ -16438,7 +16434,7 @@
         <v>1036999999999999.9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>340</v>
       </c>
@@ -16579,7 +16575,7 @@
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>341</v>
       </c>
@@ -16686,7 +16682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>342</v>
       </c>
@@ -16793,7 +16789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>343</v>
       </c>
@@ -16900,7 +16896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>325</v>
       </c>
@@ -17041,7 +17037,7 @@
         <v>17906000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>326</v>
       </c>
@@ -17182,7 +17178,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>327</v>
       </c>
@@ -17323,7 +17319,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>328</v>
       </c>
@@ -17464,7 +17460,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>329</v>
       </c>
@@ -17605,7 +17601,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>371</v>
       </c>
@@ -17746,7 +17742,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>347</v>
       </c>
@@ -17887,7 +17883,7 @@
         <v>3142000000000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>344</v>
       </c>
@@ -17994,7 +17990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>330</v>
       </c>
@@ -18135,7 +18131,7 @@
         <v>12992301971719.6</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -18276,7 +18272,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>368</v>
       </c>
@@ -18417,7 +18413,7 @@
         <v>5810700000000</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>369</v>
       </c>
@@ -18558,7 +18554,7 @@
         <v>91410000000</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>370</v>
       </c>
@@ -18699,7 +18695,7 @@
         <v>13583444584264.561</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>366</v>
       </c>
@@ -18851,14 +18847,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.81640625" style="2" customWidth="1"/>
     <col min="2" max="35" width="10" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9.1640625" style="2"/>
+    <col min="36" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
@@ -18965,7 +18961,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>352</v>
       </c>
@@ -19106,7 +19102,7 @@
         <v>3142000</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>323</v>
       </c>
@@ -19247,7 +19243,7 @@
         <v>19887484</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>324</v>
       </c>
@@ -19388,7 +19384,7 @@
         <v>1036999.9999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>358</v>
       </c>
@@ -19529,7 +19525,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>341</v>
       </c>
@@ -19636,7 +19632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>342</v>
       </c>
@@ -19743,7 +19739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>343</v>
       </c>
@@ -19850,7 +19846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>325</v>
       </c>
@@ -19991,7 +19987,7 @@
         <v>17906000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>326</v>
       </c>
@@ -20132,7 +20128,7 @@
         <v>119596.09523809524</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>327</v>
       </c>
@@ -20273,7 +20269,7 @@
         <v>138690.47619047618</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>328</v>
       </c>
@@ -20414,7 +20410,7 @@
         <v>94981.738095238092</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>329</v>
       </c>
@@ -20555,7 +20551,7 @@
         <v>127595.23809523809</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>371</v>
       </c>
@@ -20696,7 +20692,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>353</v>
       </c>
@@ -20837,7 +20833,7 @@
         <v>3142000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>344</v>
       </c>
@@ -20944,7 +20940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>330</v>
       </c>
@@ -21085,7 +21081,7 @@
         <v>12992301.9717196</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>367</v>
       </c>
@@ -21226,7 +21222,7 @@
         <v>5810700</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>368</v>
       </c>
@@ -21367,7 +21363,7 @@
         <v>5810700</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>369</v>
       </c>
@@ -21508,7 +21504,7 @@
         <v>91410</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>370</v>
       </c>
@@ -21649,7 +21645,7 @@
         <v>13583444.58426456</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>366</v>
       </c>
@@ -21801,13 +21797,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="1" max="1" width="38.26953125" customWidth="1"/>
     <col min="2" max="35" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>403</v>
       </c>
@@ -21914,7 +21910,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>310</v>
       </c>
@@ -22021,7 +22017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>311</v>
       </c>
@@ -22128,7 +22124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>318</v>
       </c>
@@ -22269,7 +22265,7 @@
         <v>119596.09523809524</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>319</v>
       </c>
@@ -22410,7 +22406,7 @@
         <v>138690.47619047618</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>312</v>
       </c>
@@ -22517,7 +22513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>313</v>
       </c>
@@ -22624,7 +22620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>320</v>
       </c>
@@ -22765,7 +22761,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>400</v>
       </c>
@@ -22872,7 +22868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>369</v>
       </c>
@@ -22979,7 +22975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>366</v>
       </c>
@@ -23097,14 +23093,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>299</v>
       </c>
